--- a/artfynd/A 32502-2026 artfynd.xlsx
+++ b/artfynd/A 32502-2026 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>136293882</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136293891</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>136293892</v>
       </c>
       <c r="B8" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136293895</v>
       </c>
       <c r="B9" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136293881</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136293887</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>136293888</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
